--- a/EXCEL/Classwork/FUCNTION AND FORMULA ON E-COMMERCE DATA.xlsx
+++ b/EXCEL/Classwork/FUCNTION AND FORMULA ON E-COMMERCE DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ANUDIP_BY_SAYAR_DPBA\EXCEL\Classwork\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A018F15F-68AE-4CFE-9640-E659C64BC7D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5A6965-C84D-4985-B8E0-F57303A5BB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Function &amp; Formula Used" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2650" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2694" uniqueCount="107">
   <si>
     <t>Order ID</t>
   </si>
@@ -358,12 +358,36 @@
   <si>
     <t>Fail</t>
   </si>
+  <si>
+    <t>Brand Name</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Sakrajit</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Product Rows</t>
+  </si>
+  <si>
+    <t>Unit sold rows</t>
+  </si>
+  <si>
+    <t>Countblank</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -371,16 +395,42 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -403,15 +453,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -692,69 +762,73 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V373"/>
+  <dimension ref="A1:X373"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -770,7 +844,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>10001</v>
       </c>
@@ -826,11 +900,11 @@
         <v>Low</v>
       </c>
       <c r="R2" s="1" t="str">
-        <f>IF(L2&gt;=7,"High",IF(L2&gt;=5,"Medium","Low"))</f>
-        <v>High</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+        <f>IF(L2&gt;8,"High",IF(L2&gt;4,"Medium","Low"))</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>10002</v>
       </c>
@@ -886,11 +960,11 @@
         <v>Medium</v>
       </c>
       <c r="R3" s="1" t="str">
-        <f t="shared" ref="R3:R66" si="2">IF(L3&gt;=7,"High",IF(L3&gt;=5,"Medium","Low"))</f>
-        <v>High</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+        <f t="shared" ref="R3:R66" si="2">IF(L3&gt;8,"High",IF(L3&gt;4,"Medium","Low"))</f>
+        <v>High</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>10003</v>
       </c>
@@ -950,7 +1024,7 @@
         <v>Medium</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>10004</v>
       </c>
@@ -1010,7 +1084,7 @@
         <v>Low</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>10005</v>
       </c>
@@ -1067,18 +1141,18 @@
       </c>
       <c r="R6" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>High</v>
-      </c>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1" t="s">
+        <v>Medium</v>
+      </c>
+      <c r="T6" s="4"/>
+      <c r="W6" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="V6" s="1">
+      <c r="X6" s="1">
         <f>SUM(L2:L373)</f>
         <v>1837</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>10006</v>
       </c>
@@ -1137,11 +1211,12 @@
         <f t="shared" si="2"/>
         <v>Low</v>
       </c>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1"/>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="5"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>10007</v>
       </c>
@@ -1200,18 +1275,18 @@
         <f t="shared" si="2"/>
         <v>Medium</v>
       </c>
-      <c r="T8" s="1" t="s">
+      <c r="V8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="U8" s="1" t="s">
+      <c r="W8" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="V8" s="1">
-        <f>SUMIF(K2:K373,T8,L2:L373)</f>
+      <c r="X8" s="1">
+        <f>SUMIF(K2:K373,V8,L2:L373)</f>
         <v>369</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>10008</v>
       </c>
@@ -1271,7 +1346,7 @@
         <v>Low</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>10009</v>
       </c>
@@ -1330,8 +1405,17 @@
         <f t="shared" si="2"/>
         <v>Medium</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="U10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10010</v>
       </c>
@@ -1390,8 +1474,18 @@
         <f t="shared" si="2"/>
         <v>Medium</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="U11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="W11" s="1">
+        <f>SUMIFS(L2:L373,I2:I373,U11,K2:K373,V11)</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10011</v>
       </c>
@@ -1451,7 +1545,7 @@
         <v>Medium</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>10012</v>
       </c>
@@ -1510,8 +1604,18 @@
         <f t="shared" si="2"/>
         <v>Medium</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="U13" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="V13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="W13" s="6">
+        <f>AVERAGE(M2:M373)</f>
+        <v>2001.1641935483883</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>10013</v>
       </c>
@@ -1568,10 +1672,20 @@
       </c>
       <c r="R14" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>High</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+        <v>Medium</v>
+      </c>
+      <c r="U14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="V14" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="W14" s="9">
+        <f>AVERAGEIF(K2:K373,U14,M2:M373)</f>
+        <v>1859.1251898734179</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>10014</v>
       </c>
@@ -1628,10 +1742,20 @@
       </c>
       <c r="R15" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>High</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+        <v>Medium</v>
+      </c>
+      <c r="V15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="W15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="X15" s="10">
+        <f>AVERAGEIFS(O2:O373,I2:I373,V15,K2:K373,W15)</f>
+        <v>17983.055</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>10015</v>
       </c>
@@ -1691,7 +1815,7 @@
         <v>High</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>10016</v>
       </c>
@@ -1748,10 +1872,13 @@
       </c>
       <c r="R17" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>High</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+        <v>Medium</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>10017</v>
       </c>
@@ -1810,8 +1937,11 @@
         <f t="shared" si="2"/>
         <v>Low</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U18" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>10018</v>
       </c>
@@ -1870,8 +2000,11 @@
         <f t="shared" si="2"/>
         <v>Low</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U19" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>10019</v>
       </c>
@@ -1930,8 +2063,11 @@
         <f t="shared" si="2"/>
         <v>Low</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U20" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>10020</v>
       </c>
@@ -1990,8 +2126,12 @@
         <f t="shared" si="2"/>
         <v>Low</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U21" s="1"/>
+      <c r="V21" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>10021</v>
       </c>
@@ -2050,8 +2190,12 @@
         <f t="shared" si="2"/>
         <v>Low</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U22" s="1">
+        <f>AVERAGE(U18:U20)</f>
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>10022</v>
       </c>
@@ -2108,10 +2252,10 @@
       </c>
       <c r="R23" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>High</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>10023</v>
       </c>
@@ -2171,7 +2315,7 @@
         <v>Low</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>10024</v>
       </c>
@@ -2231,7 +2375,7 @@
         <v>Low</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>10025</v>
       </c>
@@ -2290,8 +2434,20 @@
         <f t="shared" si="2"/>
         <v>Medium</v>
       </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="V26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="W26" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="X26" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>10026</v>
       </c>
@@ -2350,8 +2506,20 @@
         <f t="shared" si="2"/>
         <v>High</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W27" s="1">
+        <v>7</v>
+      </c>
+      <c r="X27" s="1">
+        <v>2843.87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>10027</v>
       </c>
@@ -2410,8 +2578,20 @@
         <f t="shared" si="2"/>
         <v>Low</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W28" s="1">
+        <v>9</v>
+      </c>
+      <c r="X28" s="1">
+        <v>2525.23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>10028</v>
       </c>
@@ -2470,8 +2650,20 @@
         <f t="shared" si="2"/>
         <v>Medium</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="W29" s="1">
+        <v>6</v>
+      </c>
+      <c r="X29" s="1">
+        <v>3474.34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>10029</v>
       </c>
@@ -2530,8 +2722,18 @@
         <f t="shared" si="2"/>
         <v>Low</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="V30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W30" s="1"/>
+      <c r="X30" s="1">
+        <v>1008.79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>10030</v>
       </c>
@@ -2590,8 +2792,20 @@
         <f t="shared" si="2"/>
         <v>Low</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="V31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W31" s="1">
+        <v>7</v>
+      </c>
+      <c r="X31" s="1">
+        <v>3511.47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>10031</v>
       </c>
@@ -2650,8 +2864,20 @@
         <f t="shared" si="2"/>
         <v>Medium</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="W32" s="1">
+        <v>3</v>
+      </c>
+      <c r="X32" s="1">
+        <v>3189.55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>10032</v>
       </c>
@@ -2710,8 +2936,18 @@
         <f t="shared" si="2"/>
         <v>Low</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1">
+        <v>3030.42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>10033</v>
       </c>
@@ -2768,10 +3004,22 @@
       </c>
       <c r="R34" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>High</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+        <v>Medium</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="W34" s="1">
+        <v>4</v>
+      </c>
+      <c r="X34" s="1">
+        <v>2310.83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>10034</v>
       </c>
@@ -2830,8 +3078,20 @@
         <f t="shared" si="2"/>
         <v>Medium</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U35" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="V35" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W35" s="1">
+        <v>5</v>
+      </c>
+      <c r="X35" s="1">
+        <v>1098.04</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>10035</v>
       </c>
@@ -2888,10 +3148,22 @@
       </c>
       <c r="R36" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>High</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+        <v>Medium</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="W36" s="1">
+        <v>5</v>
+      </c>
+      <c r="X36" s="1">
+        <v>1780.66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>10036</v>
       </c>
@@ -2951,7 +3223,7 @@
         <v>Medium</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>10037</v>
       </c>
@@ -3011,7 +3283,7 @@
         <v>Low</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>10038</v>
       </c>
@@ -3068,10 +3340,10 @@
       </c>
       <c r="R39" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>High</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>10039</v>
       </c>
@@ -3128,10 +3400,10 @@
       </c>
       <c r="R40" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>High</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>10040</v>
       </c>
@@ -3191,7 +3463,7 @@
         <v>Medium</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>10041</v>
       </c>
@@ -3248,10 +3520,20 @@
       </c>
       <c r="R42" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>High</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+        <v>Medium</v>
+      </c>
+      <c r="U42" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="V42" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="W42" s="1">
+        <f>COUNTA(U27:U36)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>10042</v>
       </c>
@@ -3310,8 +3592,15 @@
         <f t="shared" si="2"/>
         <v>Low</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="V43" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="W43" s="1">
+        <f>COUNT(W27:W36)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>10043</v>
       </c>
@@ -3371,7 +3660,7 @@
         <v>Medium</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>10044</v>
       </c>
@@ -3430,8 +3719,16 @@
         <f t="shared" si="2"/>
         <v>Low</v>
       </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U45" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="V45" s="10"/>
+      <c r="W45" s="10">
+        <f>COUNTBLANK(W27:W36)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>10045</v>
       </c>
@@ -3491,7 +3788,7 @@
         <v>Low</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>10046</v>
       </c>
@@ -3548,10 +3845,18 @@
       </c>
       <c r="R47" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>High</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+        <v>Medium</v>
+      </c>
+      <c r="U47" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="V47" s="1">
+        <f>COUNTIF(K2:K373,U47)</f>
+        <v>75</v>
+      </c>
+      <c r="W47" s="1"/>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>10047</v>
       </c>
@@ -3610,6 +3915,16 @@
         <f t="shared" si="2"/>
         <v>Low</v>
       </c>
+      <c r="U48" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="V48" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="W48" s="1">
+        <f>COUNTIFS(I2:I373,U48,K2:K373,V48)</f>
+        <v>6</v>
+      </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
@@ -3968,7 +4283,7 @@
       </c>
       <c r="R54" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
@@ -4208,7 +4523,7 @@
       </c>
       <c r="R58" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
@@ -4268,7 +4583,7 @@
       </c>
       <c r="R59" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
@@ -4328,7 +4643,7 @@
       </c>
       <c r="R60" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
@@ -4568,7 +4883,7 @@
       </c>
       <c r="R64" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.3">
@@ -4747,7 +5062,7 @@
         <v>Medium</v>
       </c>
       <c r="R67" s="1" t="str">
-        <f t="shared" ref="R67:R130" si="5">IF(L67&gt;=7,"High",IF(L67&gt;=5,"Medium","Low"))</f>
+        <f t="shared" ref="R67:R130" si="5">IF(L67&gt;8,"High",IF(L67&gt;4,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
     </row>
@@ -5528,7 +5843,7 @@
       </c>
       <c r="R80" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.3">
@@ -5768,7 +6083,7 @@
       </c>
       <c r="R84" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.3">
@@ -6428,7 +6743,7 @@
       </c>
       <c r="R95" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.3">
@@ -6488,7 +6803,7 @@
       </c>
       <c r="R96" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.3">
@@ -6608,7 +6923,7 @@
       </c>
       <c r="R98" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.3">
@@ -7268,7 +7583,7 @@
       </c>
       <c r="R109" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.3">
@@ -7448,7 +7763,7 @@
       </c>
       <c r="R112" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.3">
@@ -7508,7 +7823,7 @@
       </c>
       <c r="R113" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.3">
@@ -7688,7 +8003,7 @@
       </c>
       <c r="R116" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.3">
@@ -8168,7 +8483,7 @@
       </c>
       <c r="R124" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.3">
@@ -8587,7 +8902,7 @@
         <v>High</v>
       </c>
       <c r="R131" s="1" t="str">
-        <f t="shared" ref="R131:R194" si="8">IF(L131&gt;=7,"High",IF(L131&gt;=5,"Medium","Low"))</f>
+        <f t="shared" ref="R131:R194" si="8">IF(L131&gt;8,"High",IF(L131&gt;4,"Medium","Low"))</f>
         <v>Low</v>
       </c>
     </row>
@@ -8768,7 +9083,7 @@
       </c>
       <c r="R134" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.3">
@@ -8828,7 +9143,7 @@
       </c>
       <c r="R135" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.3">
@@ -9128,7 +9443,7 @@
       </c>
       <c r="R140" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.3">
@@ -9548,7 +9863,7 @@
       </c>
       <c r="R147" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.3">
@@ -9608,7 +9923,7 @@
       </c>
       <c r="R148" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.3">
@@ -9788,7 +10103,7 @@
       </c>
       <c r="R151" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.3">
@@ -9848,7 +10163,7 @@
       </c>
       <c r="R152" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.3">
@@ -10088,7 +10403,7 @@
       </c>
       <c r="R156" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.3">
@@ -10148,7 +10463,7 @@
       </c>
       <c r="R157" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.3">
@@ -10208,7 +10523,7 @@
       </c>
       <c r="R158" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.3">
@@ -10268,7 +10583,7 @@
       </c>
       <c r="R159" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.3">
@@ -10328,7 +10643,7 @@
       </c>
       <c r="R160" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.3">
@@ -10628,7 +10943,7 @@
       </c>
       <c r="R165" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.3">
@@ -10748,7 +11063,7 @@
       </c>
       <c r="R167" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.3">
@@ -10868,7 +11183,7 @@
       </c>
       <c r="R169" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.3">
@@ -10988,7 +11303,7 @@
       </c>
       <c r="R171" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="172" spans="1:18" x14ac:dyDescent="0.3">
@@ -11288,7 +11603,7 @@
       </c>
       <c r="R176" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="177" spans="1:18" x14ac:dyDescent="0.3">
@@ -11588,7 +11903,7 @@
       </c>
       <c r="R181" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.3">
@@ -12008,7 +12323,7 @@
       </c>
       <c r="R188" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="189" spans="1:18" x14ac:dyDescent="0.3">
@@ -12068,7 +12383,7 @@
       </c>
       <c r="R189" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="190" spans="1:18" x14ac:dyDescent="0.3">
@@ -12128,7 +12443,7 @@
       </c>
       <c r="R190" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="191" spans="1:18" x14ac:dyDescent="0.3">
@@ -12188,7 +12503,7 @@
       </c>
       <c r="R191" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="192" spans="1:18" x14ac:dyDescent="0.3">
@@ -12248,7 +12563,7 @@
       </c>
       <c r="R192" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="193" spans="1:18" x14ac:dyDescent="0.3">
@@ -12427,7 +12742,7 @@
         <v>High</v>
       </c>
       <c r="R195" s="1" t="str">
-        <f t="shared" ref="R195:R258" si="11">IF(L195&gt;=7,"High",IF(L195&gt;=5,"Medium","Low"))</f>
+        <f t="shared" ref="R195:R258" si="11">IF(L195&gt;8,"High",IF(L195&gt;4,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
     </row>
@@ -12668,7 +12983,7 @@
       </c>
       <c r="R199" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.3">
@@ -12728,7 +13043,7 @@
       </c>
       <c r="R200" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="201" spans="1:18" x14ac:dyDescent="0.3">
@@ -12908,7 +13223,7 @@
       </c>
       <c r="R203" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.3">
@@ -13088,7 +13403,7 @@
       </c>
       <c r="R206" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.3">
@@ -13208,7 +13523,7 @@
       </c>
       <c r="R208" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.3">
@@ -13568,7 +13883,7 @@
       </c>
       <c r="R214" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="215" spans="1:18" x14ac:dyDescent="0.3">
@@ -13688,7 +14003,7 @@
       </c>
       <c r="R216" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="217" spans="1:18" x14ac:dyDescent="0.3">
@@ -13748,7 +14063,7 @@
       </c>
       <c r="R217" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="218" spans="1:18" x14ac:dyDescent="0.3">
@@ -13868,7 +14183,7 @@
       </c>
       <c r="R219" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="220" spans="1:18" x14ac:dyDescent="0.3">
@@ -14288,7 +14603,7 @@
       </c>
       <c r="R226" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="227" spans="1:18" x14ac:dyDescent="0.3">
@@ -14348,7 +14663,7 @@
       </c>
       <c r="R227" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="228" spans="1:18" x14ac:dyDescent="0.3">
@@ -14468,7 +14783,7 @@
       </c>
       <c r="R229" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="230" spans="1:18" x14ac:dyDescent="0.3">
@@ -14948,7 +15263,7 @@
       </c>
       <c r="R237" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="238" spans="1:18" x14ac:dyDescent="0.3">
@@ -15068,7 +15383,7 @@
       </c>
       <c r="R239" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="240" spans="1:18" x14ac:dyDescent="0.3">
@@ -15308,7 +15623,7 @@
       </c>
       <c r="R243" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="244" spans="1:18" x14ac:dyDescent="0.3">
@@ -15368,7 +15683,7 @@
       </c>
       <c r="R244" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="245" spans="1:18" x14ac:dyDescent="0.3">
@@ -15668,7 +15983,7 @@
       </c>
       <c r="R249" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="250" spans="1:18" x14ac:dyDescent="0.3">
@@ -16267,7 +16582,7 @@
         <v>High</v>
       </c>
       <c r="R259" s="1" t="str">
-        <f t="shared" ref="R259:R322" si="14">IF(L259&gt;=7,"High",IF(L259&gt;=5,"Medium","Low"))</f>
+        <f t="shared" ref="R259:R322" si="14">IF(L259&gt;8,"High",IF(L259&gt;4,"Medium","Low"))</f>
         <v>Low</v>
       </c>
     </row>
@@ -16388,7 +16703,7 @@
       </c>
       <c r="R261" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="262" spans="1:18" x14ac:dyDescent="0.3">
@@ -16448,7 +16763,7 @@
       </c>
       <c r="R262" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="263" spans="1:18" x14ac:dyDescent="0.3">
@@ -16568,7 +16883,7 @@
       </c>
       <c r="R264" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="265" spans="1:18" x14ac:dyDescent="0.3">
@@ -16628,7 +16943,7 @@
       </c>
       <c r="R265" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="266" spans="1:18" x14ac:dyDescent="0.3">
@@ -16688,7 +17003,7 @@
       </c>
       <c r="R266" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="267" spans="1:18" x14ac:dyDescent="0.3">
@@ -16868,7 +17183,7 @@
       </c>
       <c r="R269" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="270" spans="1:18" x14ac:dyDescent="0.3">
@@ -17168,7 +17483,7 @@
       </c>
       <c r="R274" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="275" spans="1:18" x14ac:dyDescent="0.3">
@@ -17588,7 +17903,7 @@
       </c>
       <c r="R281" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="282" spans="1:18" x14ac:dyDescent="0.3">
@@ -18128,7 +18443,7 @@
       </c>
       <c r="R290" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="291" spans="1:18" x14ac:dyDescent="0.3">
@@ -18188,7 +18503,7 @@
       </c>
       <c r="R291" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="292" spans="1:18" x14ac:dyDescent="0.3">
@@ -18308,7 +18623,7 @@
       </c>
       <c r="R293" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="294" spans="1:18" x14ac:dyDescent="0.3">
@@ -18548,7 +18863,7 @@
       </c>
       <c r="R297" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="298" spans="1:18" x14ac:dyDescent="0.3">
@@ -18608,7 +18923,7 @@
       </c>
       <c r="R298" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="299" spans="1:18" x14ac:dyDescent="0.3">
@@ -19388,7 +19703,7 @@
       </c>
       <c r="R311" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="312" spans="1:18" x14ac:dyDescent="0.3">
@@ -19628,7 +19943,7 @@
       </c>
       <c r="R315" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="316" spans="1:18" x14ac:dyDescent="0.3">
@@ -20107,7 +20422,7 @@
         <v>Low</v>
       </c>
       <c r="R323" s="1" t="str">
-        <f t="shared" ref="R323:R373" si="17">IF(L323&gt;=7,"High",IF(L323&gt;=5,"Medium","Low"))</f>
+        <f t="shared" ref="R323:R373" si="17">IF(L323&gt;8,"High",IF(L323&gt;4,"Medium","Low"))</f>
         <v>Low</v>
       </c>
     </row>
@@ -20228,7 +20543,7 @@
       </c>
       <c r="R325" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="326" spans="1:18" x14ac:dyDescent="0.3">
@@ -20348,7 +20663,7 @@
       </c>
       <c r="R327" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="328" spans="1:18" x14ac:dyDescent="0.3">
@@ -20528,7 +20843,7 @@
       </c>
       <c r="R330" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="331" spans="1:18" x14ac:dyDescent="0.3">
@@ -20828,7 +21143,7 @@
       </c>
       <c r="R335" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="336" spans="1:18" x14ac:dyDescent="0.3">
@@ -21428,7 +21743,7 @@
       </c>
       <c r="R345" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="346" spans="1:18" x14ac:dyDescent="0.3">
@@ -22088,7 +22403,7 @@
       </c>
       <c r="R356" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="357" spans="1:18" x14ac:dyDescent="0.3">
@@ -22268,7 +22583,7 @@
       </c>
       <c r="R359" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="360" spans="1:18" x14ac:dyDescent="0.3">
@@ -22328,7 +22643,7 @@
       </c>
       <c r="R360" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="361" spans="1:18" x14ac:dyDescent="0.3">
@@ -22568,7 +22883,7 @@
       </c>
       <c r="R364" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="365" spans="1:18" x14ac:dyDescent="0.3">
@@ -22628,7 +22943,7 @@
       </c>
       <c r="R365" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="366" spans="1:18" x14ac:dyDescent="0.3">
@@ -22748,7 +23063,7 @@
       </c>
       <c r="R367" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="368" spans="1:18" x14ac:dyDescent="0.3">
@@ -22868,7 +23183,7 @@
       </c>
       <c r="R369" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="370" spans="1:18" x14ac:dyDescent="0.3">
@@ -23113,6 +23428,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -23179,23 +23495,23 @@
       </c>
       <c r="B3" s="1">
         <f t="shared" ref="B3:B9" ca="1" si="0">RANDBETWEEN(40,100)</f>
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C3" s="1">
         <f t="shared" ref="C3:D9" ca="1" si="1">RANDBETWEEN(40,100)</f>
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="D3" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="E3" s="1">
         <f t="shared" ref="E3:E9" ca="1" si="2">SUM(B3:D3)</f>
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="F3" s="1">
         <f t="shared" ref="F3:F9" ca="1" si="3">AVERAGE(E3/3)</f>
-        <v>59</v>
+        <v>69.666666666666671</v>
       </c>
       <c r="G3" s="1" t="str">
         <f t="shared" ref="G3:G8" ca="1" si="4">IF(F3&gt;=90,"A",IF(F3&gt;=70,"B",IF(F3&gt;=50,"C",IF(F3&gt;=40,"Pass",IF(F3&lt;40,"Fail")))))</f>
@@ -23208,27 +23524,27 @@
       </c>
       <c r="B4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D4" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="F4" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>58</v>
+        <v>70.333333333333329</v>
       </c>
       <c r="G4" s="1" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -23237,23 +23553,23 @@
       </c>
       <c r="B5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="F5" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>83.666666666666671</v>
+        <v>78</v>
       </c>
       <c r="G5" s="1" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -23266,23 +23582,23 @@
       </c>
       <c r="B6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="F6" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>72.333333333333329</v>
+        <v>74.333333333333329</v>
       </c>
       <c r="G6" s="1" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -23321,27 +23637,27 @@
       </c>
       <c r="B8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>211</v>
+        <v>279</v>
       </c>
       <c r="F8" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>70.333333333333329</v>
+        <v>93</v>
       </c>
       <c r="G8" s="1" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -23350,27 +23666,27 @@
       </c>
       <c r="B9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="D9" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>189</v>
+        <v>258</v>
       </c>
       <c r="F9" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="G9" s="1" t="str">
         <f ca="1">IF(IF9&gt;=90,"A",IF(F9&gt;=70,"B",IF(F9&gt;=50,"C",IF(F9&gt;=40,"Pass",IF(F9&lt;40,"Fail")))))</f>
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">

--- a/EXCEL/Classwork/FUCNTION AND FORMULA ON E-COMMERCE DATA.xlsx
+++ b/EXCEL/Classwork/FUCNTION AND FORMULA ON E-COMMERCE DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ANUDIP_BY_SAYAR_DPBA\EXCEL\Classwork\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5A6965-C84D-4985-B8E0-F57303A5BB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71F4BFC-017F-4D60-A752-40239939E4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1848" yWindow="1848" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Function &amp; Formula Used" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2694" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2703" uniqueCount="109">
   <si>
     <t>Order ID</t>
   </si>
@@ -365,9 +365,6 @@
     <t>Product</t>
   </si>
   <si>
-    <t>Sakrajit</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -381,6 +378,15 @@
   </si>
   <si>
     <t>Countblank</t>
+  </si>
+  <si>
+    <t>Sayar</t>
+  </si>
+  <si>
+    <t>Total Sale Ammount</t>
+  </si>
+  <si>
+    <t>Total Sale Ammount(Using SUMPRODUCT)</t>
   </si>
 </sst>
 </file>
@@ -774,7 +780,7 @@
     <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.21875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.21875" bestFit="1" customWidth="1"/>
@@ -783,9 +789,10 @@
     <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="49.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.88671875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
@@ -1875,7 +1882,7 @@
         <v>Medium</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
@@ -2128,7 +2135,7 @@
       </c>
       <c r="U21" s="1"/>
       <c r="V21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
@@ -3523,10 +3530,10 @@
         <v>Medium</v>
       </c>
       <c r="U42" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="V42" s="10" t="s">
         <v>103</v>
-      </c>
-      <c r="V42" s="10" t="s">
-        <v>104</v>
       </c>
       <c r="W42" s="1">
         <f>COUNTA(U27:U36)</f>
@@ -3593,7 +3600,7 @@
         <v>Low</v>
       </c>
       <c r="V43" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W43" s="1">
         <f>COUNT(W27:W36)</f>
@@ -3720,7 +3727,7 @@
         <v>Low</v>
       </c>
       <c r="U45" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="V45" s="10"/>
       <c r="W45" s="10">
@@ -3926,7 +3933,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>10048</v>
       </c>
@@ -3986,7 +3993,7 @@
         <v>Medium</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>10049</v>
       </c>
@@ -4046,7 +4053,7 @@
         <v>Medium</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>10050</v>
       </c>
@@ -4106,7 +4113,7 @@
         <v>Medium</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>10052</v>
       </c>
@@ -4165,8 +4172,15 @@
         <f t="shared" si="2"/>
         <v>Low</v>
       </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U52" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="V52" s="1">
+        <f>SUM(O2:O373)</f>
+        <v>3664518.5400000005</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>10053</v>
       </c>
@@ -4226,7 +4240,7 @@
         <v>Medium</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>10054</v>
       </c>
@@ -4286,7 +4300,7 @@
         <v>Medium</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>10055</v>
       </c>
@@ -4345,8 +4359,15 @@
         <f t="shared" si="2"/>
         <v>Low</v>
       </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U55" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="V55" s="1">
+        <f>SUMPRODUCT(L2:L373,M2:M373)</f>
+        <v>3664518.5400000005</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>10056</v>
       </c>
@@ -4406,7 +4427,7 @@
         <v>Medium</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>10057</v>
       </c>
@@ -4466,7 +4487,7 @@
         <v>High</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>10059</v>
       </c>
@@ -4525,8 +4546,18 @@
         <f t="shared" si="2"/>
         <v>Medium</v>
       </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U58" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="V58" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="W58" s="1" cm="1">
+        <f t="array" ref="W58">SUMPRODUCT($L$2:$L$373,$M$2:$M$373,--($K$2:$K$373=V58))</f>
+        <v>737855.54000000015</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>10060</v>
       </c>
@@ -4585,8 +4616,16 @@
         <f t="shared" si="2"/>
         <v>Medium</v>
       </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U59" s="1"/>
+      <c r="V59" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="W59" s="1" cm="1">
+        <f t="array" ref="W59">SUMPRODUCT($L$2:$L$373,$M$2:$M$373,--($K$2:$K$373=V59))</f>
+        <v>754015.00999999989</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>10061</v>
       </c>
@@ -4645,8 +4684,16 @@
         <f t="shared" si="2"/>
         <v>Medium</v>
       </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U60" s="1"/>
+      <c r="V60" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="W60" s="1" cm="1">
+        <f t="array" ref="W60">SUMPRODUCT($L$2:$L$373,$M$2:$M$373,--($K$2:$K$373=V60))</f>
+        <v>678192.21</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>10063</v>
       </c>
@@ -4705,8 +4752,16 @@
         <f t="shared" si="2"/>
         <v>Medium</v>
       </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U61" s="1"/>
+      <c r="V61" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="W61" s="1" cm="1">
+        <f t="array" ref="W61">SUMPRODUCT($L$2:$L$373,$M$2:$M$373,--($K$2:$K$373=V61))</f>
+        <v>608728.77999999991</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>10064</v>
       </c>
@@ -4765,8 +4820,16 @@
         <f t="shared" si="2"/>
         <v>Low</v>
       </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U62" s="1"/>
+      <c r="V62" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="W62" s="1" cm="1">
+        <f t="array" ref="W62">SUMPRODUCT($L$2:$L$373,$M$2:$M$373,--($K$2:$K$373=V62))</f>
+        <v>885726.99999999988</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>10065</v>
       </c>
@@ -4825,8 +4888,16 @@
         <f t="shared" si="2"/>
         <v>Low</v>
       </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="U63" s="1"/>
+      <c r="V63" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="W63" s="1">
+        <f>SUM(W58:W62)</f>
+        <v>3664518.5399999996</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>10066</v>
       </c>
@@ -23481,7 +23552,7 @@
         <v>270</v>
       </c>
       <c r="F2" s="1">
-        <f>AVERAGE(E2/3)</f>
+        <f>AVERAGE(B2:D2)</f>
         <v>90</v>
       </c>
       <c r="G2" s="1" t="str">
@@ -23495,27 +23566,27 @@
       </c>
       <c r="B3" s="1">
         <f t="shared" ref="B3:B9" ca="1" si="0">RANDBETWEEN(40,100)</f>
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C3" s="1">
         <f t="shared" ref="C3:D9" ca="1" si="1">RANDBETWEEN(40,100)</f>
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="D3" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="E3" s="1">
         <f t="shared" ref="E3:E9" ca="1" si="2">SUM(B3:D3)</f>
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F3" s="1">
-        <f t="shared" ref="F3:F9" ca="1" si="3">AVERAGE(E3/3)</f>
-        <v>69.666666666666671</v>
+        <f t="shared" ref="F3:F9" ca="1" si="3">AVERAGE(B3:D3)</f>
+        <v>70.666666666666671</v>
       </c>
       <c r="G3" s="1" t="str">
         <f t="shared" ref="G3:G8" ca="1" si="4">IF(F3&gt;=90,"A",IF(F3&gt;=70,"B",IF(F3&gt;=50,"C",IF(F3&gt;=40,"Pass",IF(F3&lt;40,"Fail")))))</f>
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -23524,23 +23595,23 @@
       </c>
       <c r="B4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="D4" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="F4" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>70.333333333333329</v>
+        <v>82.666666666666671</v>
       </c>
       <c r="G4" s="1" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -23553,23 +23624,23 @@
       </c>
       <c r="B5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F5" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>78</v>
+        <v>78.333333333333329</v>
       </c>
       <c r="G5" s="1" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -23582,23 +23653,23 @@
       </c>
       <c r="B6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>223</v>
+        <v>261</v>
       </c>
       <c r="F6" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>74.333333333333329</v>
+        <v>87</v>
       </c>
       <c r="G6" s="1" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -23637,27 +23708,27 @@
       </c>
       <c r="B8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>279</v>
+        <v>234</v>
       </c>
       <c r="F8" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="G8" s="1" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -23666,27 +23737,27 @@
       </c>
       <c r="B9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="D9" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>258</v>
+        <v>165</v>
       </c>
       <c r="F9" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="G9" s="1" t="str">
         <f ca="1">IF(IF9&gt;=90,"A",IF(F9&gt;=70,"B",IF(F9&gt;=50,"C",IF(F9&gt;=40,"Pass",IF(F9&lt;40,"Fail")))))</f>
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
